--- a/artfynd/A 43194-2024 artfynd.xlsx
+++ b/artfynd/A 43194-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120487646</v>
+        <v>120487651</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Piltäppmyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437373</v>
+        <v>437319</v>
       </c>
       <c r="R2" t="n">
-        <v>6758397</v>
+        <v>6758396</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120487651</v>
+        <v>120487654</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,47 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Piltäppmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437319</v>
+        <v>437331</v>
       </c>
       <c r="R3" t="n">
-        <v>6758396</v>
+        <v>6758345</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120487652</v>
+        <v>120487618</v>
       </c>
       <c r="B4" t="n">
-        <v>78187</v>
+        <v>78576</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437408</v>
+        <v>437372</v>
       </c>
       <c r="R4" t="n">
-        <v>6758242</v>
+        <v>6758383</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120487648</v>
+        <v>120487630</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>8432</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,38 +1002,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Piltäppmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437354</v>
+        <v>437402</v>
       </c>
       <c r="R5" t="n">
-        <v>6758398</v>
+        <v>6758419</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120487649</v>
+        <v>120487652</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437357</v>
+        <v>437408</v>
       </c>
       <c r="R6" t="n">
-        <v>6758416</v>
+        <v>6758242</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1199,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120487645</v>
+        <v>120487641</v>
       </c>
       <c r="B7" t="n">
         <v>78542</v>
@@ -1234,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437376</v>
+        <v>437319</v>
       </c>
       <c r="R7" t="n">
-        <v>6758383</v>
+        <v>6758387</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120487655</v>
+        <v>120487615</v>
       </c>
       <c r="B8" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,21 +1317,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1398,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120487633</v>
+        <v>120487614</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437355</v>
+        <v>437325</v>
       </c>
       <c r="R9" t="n">
-        <v>6758282</v>
+        <v>6758347</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120487616</v>
+        <v>120487648</v>
       </c>
       <c r="B10" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,21 +1521,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437321</v>
+        <v>437354</v>
       </c>
       <c r="R10" t="n">
-        <v>6758371</v>
+        <v>6758398</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,10 +1607,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120487656</v>
+        <v>120487647</v>
       </c>
       <c r="B11" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,21 +1623,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1647,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437335</v>
+        <v>437362</v>
       </c>
       <c r="R11" t="n">
-        <v>6758403</v>
+        <v>6758394</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,7 +1709,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120487614</v>
+        <v>120487616</v>
       </c>
       <c r="B12" t="n">
         <v>79160</v>
@@ -1744,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437325</v>
+        <v>437321</v>
       </c>
       <c r="R12" t="n">
-        <v>6758347</v>
+        <v>6758371</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120487641</v>
+        <v>120487619</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,21 +1827,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437319</v>
+        <v>437354</v>
       </c>
       <c r="R13" t="n">
-        <v>6758387</v>
+        <v>6758401</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,7 +1913,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120487657</v>
+        <v>120487658</v>
       </c>
       <c r="B14" t="n">
         <v>78187</v>
@@ -1948,10 +1953,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437367</v>
+        <v>437361</v>
       </c>
       <c r="R14" t="n">
-        <v>6758393</v>
+        <v>6758397</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,10 +2015,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120487630</v>
+        <v>120487634</v>
       </c>
       <c r="B15" t="n">
-        <v>8432</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,43 +2027,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Piltäppmyren, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437402</v>
+        <v>437400</v>
       </c>
       <c r="R15" t="n">
-        <v>6758419</v>
+        <v>6758275</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120487647</v>
+        <v>120487657</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2133,21 +2133,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437362</v>
+        <v>437367</v>
       </c>
       <c r="R16" t="n">
-        <v>6758394</v>
+        <v>6758393</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,10 +2219,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120487618</v>
+        <v>120487649</v>
       </c>
       <c r="B17" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2235,21 +2235,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437372</v>
+        <v>437357</v>
       </c>
       <c r="R17" t="n">
-        <v>6758383</v>
+        <v>6758416</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2321,7 +2321,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120487634</v>
+        <v>120487633</v>
       </c>
       <c r="B18" t="n">
         <v>78542</v>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437400</v>
+        <v>437355</v>
       </c>
       <c r="R18" t="n">
-        <v>6758275</v>
+        <v>6758282</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120487650</v>
+        <v>120487655</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,47 +2435,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Piltäppmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437321</v>
+        <v>437334</v>
       </c>
       <c r="R19" t="n">
-        <v>6758387</v>
+        <v>6758369</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2534,10 +2525,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120487658</v>
+        <v>120487645</v>
       </c>
       <c r="B20" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2550,21 +2541,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2574,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437361</v>
+        <v>437376</v>
       </c>
       <c r="R20" t="n">
-        <v>6758397</v>
+        <v>6758383</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2636,10 +2627,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120487619</v>
+        <v>120487646</v>
       </c>
       <c r="B21" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2652,21 +2643,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2676,10 +2667,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437354</v>
+        <v>437373</v>
       </c>
       <c r="R21" t="n">
-        <v>6758401</v>
+        <v>6758397</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2738,10 +2729,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120487615</v>
+        <v>120487656</v>
       </c>
       <c r="B22" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2754,21 +2745,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2778,10 +2769,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437334</v>
+        <v>437335</v>
       </c>
       <c r="R22" t="n">
-        <v>6758369</v>
+        <v>6758403</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2840,10 +2831,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120487654</v>
+        <v>120487650</v>
       </c>
       <c r="B23" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2852,38 +2843,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Piltäppmyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437331</v>
+        <v>437321</v>
       </c>
       <c r="R23" t="n">
-        <v>6758345</v>
+        <v>6758387</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 43194-2024 artfynd.xlsx
+++ b/artfynd/A 43194-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120487651</v>
+        <v>120487657</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Piltäppmyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437319</v>
+        <v>437367</v>
       </c>
       <c r="R2" t="n">
-        <v>6758396</v>
+        <v>6758393</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120487654</v>
+        <v>120487618</v>
       </c>
       <c r="B3" t="n">
-        <v>78187</v>
+        <v>78576</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437331</v>
+        <v>437372</v>
       </c>
       <c r="R3" t="n">
-        <v>6758345</v>
+        <v>6758383</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120487618</v>
+        <v>120487614</v>
       </c>
       <c r="B4" t="n">
-        <v>78576</v>
+        <v>79160</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437372</v>
+        <v>437325</v>
       </c>
       <c r="R4" t="n">
-        <v>6758383</v>
+        <v>6758347</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120487630</v>
+        <v>120487654</v>
       </c>
       <c r="B5" t="n">
-        <v>8432</v>
+        <v>78187</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,43 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Piltäppmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437402</v>
+        <v>437331</v>
       </c>
       <c r="R5" t="n">
-        <v>6758419</v>
+        <v>6758345</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120487652</v>
+        <v>120487630</v>
       </c>
       <c r="B6" t="n">
-        <v>78187</v>
+        <v>8432</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,38 +1095,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Piltäppmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437408</v>
+        <v>437402</v>
       </c>
       <c r="R6" t="n">
-        <v>6758242</v>
+        <v>6758419</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120487641</v>
+        <v>120487619</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1239,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437319</v>
+        <v>437354</v>
       </c>
       <c r="R7" t="n">
-        <v>6758387</v>
+        <v>6758401</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120487615</v>
+        <v>120487645</v>
       </c>
       <c r="B8" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437334</v>
+        <v>437376</v>
       </c>
       <c r="R8" t="n">
-        <v>6758369</v>
+        <v>6758383</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120487614</v>
+        <v>120487648</v>
       </c>
       <c r="B9" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437325</v>
+        <v>437354</v>
       </c>
       <c r="R9" t="n">
-        <v>6758347</v>
+        <v>6758398</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120487648</v>
+        <v>120487651</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,38 +1508,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Piltäppmyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437354</v>
+        <v>437319</v>
       </c>
       <c r="R10" t="n">
-        <v>6758398</v>
+        <v>6758396</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,10 +1607,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120487647</v>
+        <v>120487655</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,21 +1623,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437362</v>
+        <v>437334</v>
       </c>
       <c r="R11" t="n">
-        <v>6758394</v>
+        <v>6758369</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120487616</v>
+        <v>120487646</v>
       </c>
       <c r="B12" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,21 +1725,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437321</v>
+        <v>437373</v>
       </c>
       <c r="R12" t="n">
-        <v>6758371</v>
+        <v>6758397</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120487619</v>
+        <v>120487615</v>
       </c>
       <c r="B13" t="n">
-        <v>78576</v>
+        <v>79160</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437354</v>
+        <v>437334</v>
       </c>
       <c r="R13" t="n">
-        <v>6758401</v>
+        <v>6758369</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,7 +1913,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120487658</v>
+        <v>120487656</v>
       </c>
       <c r="B14" t="n">
         <v>78187</v>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437361</v>
+        <v>437335</v>
       </c>
       <c r="R14" t="n">
-        <v>6758397</v>
+        <v>6758403</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,10 +2015,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120487634</v>
+        <v>120487650</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,38 +2027,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Piltäppmyren, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437400</v>
+        <v>437321</v>
       </c>
       <c r="R15" t="n">
-        <v>6758275</v>
+        <v>6758387</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,10 +2126,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120487657</v>
+        <v>120487633</v>
       </c>
       <c r="B16" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2133,21 +2142,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2157,10 +2166,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437367</v>
+        <v>437355</v>
       </c>
       <c r="R16" t="n">
-        <v>6758393</v>
+        <v>6758282</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2321,7 +2330,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120487633</v>
+        <v>120487634</v>
       </c>
       <c r="B18" t="n">
         <v>78542</v>
@@ -2361,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437355</v>
+        <v>437400</v>
       </c>
       <c r="R18" t="n">
-        <v>6758282</v>
+        <v>6758275</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2423,10 +2432,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120487655</v>
+        <v>120487647</v>
       </c>
       <c r="B19" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2439,21 +2448,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2463,10 +2472,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437334</v>
+        <v>437362</v>
       </c>
       <c r="R19" t="n">
-        <v>6758369</v>
+        <v>6758394</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2525,10 +2534,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120487645</v>
+        <v>120487652</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2541,21 +2550,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2565,10 +2574,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437376</v>
+        <v>437408</v>
       </c>
       <c r="R20" t="n">
-        <v>6758383</v>
+        <v>6758242</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2627,10 +2636,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120487646</v>
+        <v>120487616</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2643,21 +2652,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2667,10 +2676,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437373</v>
+        <v>437321</v>
       </c>
       <c r="R21" t="n">
-        <v>6758397</v>
+        <v>6758371</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2729,7 +2738,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120487656</v>
+        <v>120487658</v>
       </c>
       <c r="B22" t="n">
         <v>78187</v>
@@ -2769,10 +2778,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437335</v>
+        <v>437361</v>
       </c>
       <c r="R22" t="n">
-        <v>6758403</v>
+        <v>6758397</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2831,10 +2840,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120487650</v>
+        <v>120487641</v>
       </c>
       <c r="B23" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2843,44 +2852,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Piltäppmyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437321</v>
+        <v>437319</v>
       </c>
       <c r="R23" t="n">
         <v>6758387</v>

--- a/artfynd/A 43194-2024 artfynd.xlsx
+++ b/artfynd/A 43194-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120487657</v>
+        <v>120487655</v>
       </c>
       <c r="B2" t="n">
         <v>78187</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437367</v>
+        <v>437334</v>
       </c>
       <c r="R2" t="n">
-        <v>6758393</v>
+        <v>6758369</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120487618</v>
+        <v>120487651</v>
       </c>
       <c r="B3" t="n">
-        <v>78576</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Piltäppmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437372</v>
+        <v>437319</v>
       </c>
       <c r="R3" t="n">
-        <v>6758383</v>
+        <v>6758396</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120487614</v>
+        <v>120487645</v>
       </c>
       <c r="B4" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437325</v>
+        <v>437376</v>
       </c>
       <c r="R4" t="n">
-        <v>6758347</v>
+        <v>6758383</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120487654</v>
+        <v>120487652</v>
       </c>
       <c r="B5" t="n">
         <v>78187</v>
@@ -1021,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437331</v>
+        <v>437408</v>
       </c>
       <c r="R5" t="n">
-        <v>6758345</v>
+        <v>6758242</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120487630</v>
+        <v>120487647</v>
       </c>
       <c r="B6" t="n">
-        <v>8432</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,43 +1104,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Piltäppmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437402</v>
+        <v>437362</v>
       </c>
       <c r="R6" t="n">
-        <v>6758419</v>
+        <v>6758394</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120487619</v>
+        <v>120487649</v>
       </c>
       <c r="B7" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437354</v>
+        <v>437357</v>
       </c>
       <c r="R7" t="n">
-        <v>6758401</v>
+        <v>6758416</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120487645</v>
+        <v>120487616</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437376</v>
+        <v>437321</v>
       </c>
       <c r="R8" t="n">
-        <v>6758383</v>
+        <v>6758371</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120487648</v>
+        <v>120487630</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>8432</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,38 +1410,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Piltäppmyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437354</v>
+        <v>437402</v>
       </c>
       <c r="R9" t="n">
-        <v>6758398</v>
+        <v>6758419</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120487651</v>
+        <v>120487658</v>
       </c>
       <c r="B10" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,47 +1517,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Piltäppmyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437319</v>
+        <v>437361</v>
       </c>
       <c r="R10" t="n">
-        <v>6758396</v>
+        <v>6758397</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,10 +1607,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120487655</v>
+        <v>120487646</v>
       </c>
       <c r="B11" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,21 +1623,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437334</v>
+        <v>437373</v>
       </c>
       <c r="R11" t="n">
-        <v>6758369</v>
+        <v>6758397</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120487646</v>
+        <v>120487657</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,21 +1725,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437373</v>
+        <v>437367</v>
       </c>
       <c r="R12" t="n">
-        <v>6758397</v>
+        <v>6758393</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120487615</v>
+        <v>120487654</v>
       </c>
       <c r="B13" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437334</v>
+        <v>437331</v>
       </c>
       <c r="R13" t="n">
-        <v>6758369</v>
+        <v>6758345</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,10 +1913,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120487656</v>
+        <v>120487615</v>
       </c>
       <c r="B14" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1929,21 +1929,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437335</v>
+        <v>437334</v>
       </c>
       <c r="R14" t="n">
-        <v>6758403</v>
+        <v>6758369</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,10 +2015,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120487650</v>
+        <v>120487618</v>
       </c>
       <c r="B15" t="n">
-        <v>91858</v>
+        <v>78576</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,47 +2027,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Piltäppmyren, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437321</v>
+        <v>437372</v>
       </c>
       <c r="R15" t="n">
-        <v>6758387</v>
+        <v>6758383</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,10 +2219,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120487649</v>
+        <v>120487614</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2244,21 +2235,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2268,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437357</v>
+        <v>437325</v>
       </c>
       <c r="R17" t="n">
-        <v>6758416</v>
+        <v>6758347</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2432,10 +2423,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120487647</v>
+        <v>120487650</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2444,38 +2435,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Piltäppmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437362</v>
+        <v>437321</v>
       </c>
       <c r="R19" t="n">
-        <v>6758394</v>
+        <v>6758387</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2534,7 +2534,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120487652</v>
+        <v>120487656</v>
       </c>
       <c r="B20" t="n">
         <v>78187</v>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437408</v>
+        <v>437335</v>
       </c>
       <c r="R20" t="n">
-        <v>6758242</v>
+        <v>6758403</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120487616</v>
+        <v>120487641</v>
       </c>
       <c r="B21" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2652,21 +2652,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437321</v>
+        <v>437319</v>
       </c>
       <c r="R21" t="n">
-        <v>6758371</v>
+        <v>6758387</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2738,10 +2738,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120487658</v>
+        <v>120487619</v>
       </c>
       <c r="B22" t="n">
-        <v>78187</v>
+        <v>78576</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2754,21 +2754,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437361</v>
+        <v>437354</v>
       </c>
       <c r="R22" t="n">
-        <v>6758397</v>
+        <v>6758401</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2840,7 +2840,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120487641</v>
+        <v>120487648</v>
       </c>
       <c r="B23" t="n">
         <v>78542</v>
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437319</v>
+        <v>437354</v>
       </c>
       <c r="R23" t="n">
-        <v>6758387</v>
+        <v>6758398</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
